--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001MTM.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/StandardCouponReConversionRate001MTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\guangzhoucode\tams\tams-invest-parent\tams-invest-basicdata\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-basicdata\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -13,13 +13,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="备注" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
       <rPr>
@@ -45,6 +46,9 @@
     </r>
   </si>
   <si>
+    <t>资产名称</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -54,6 +58,49 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>标准券再折算率%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>开始使用日期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>结束使用日期</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>资产代码</t>
     </r>
     <r>
@@ -67,11 +114,20 @@
       </rPr>
       <t>*</t>
     </r>
-  </si>
-  <si>
-    <t>资产名称</t>
-  </si>
-  <si>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -81,8 +137,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>标准券再折算率%</t>
-    </r>
+      <t>券商输入的是券商机构统一社会信用代码信息</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -94,11 +153,20 @@
       </rPr>
       <t>*</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>开始使用日期</t>
-    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>开始使用日期格式应为YYYYMMDD</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -110,16 +178,25 @@
       </rPr>
       <t>*</t>
     </r>
-  </si>
-  <si>
-    <t>结束使用日期</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>结束使用日期格式应为YYYYMMDD</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,6 +215,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -171,9 +255,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -492,20 +577,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -513,4 +598,31 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>